--- a/Salidas 9-6-24.xlsx
+++ b/Salidas 9-6-24.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{B8F09716-A826-8747-9DE9-FAB213905245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE5FC901-04B5-47AD-81EC-E5C0ABDE638E}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{B8F09716-A826-8747-9DE9-FAB213905245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DA820AC-3195-A141-A5CB-1D5C077449A6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,10 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
-  <si>
-    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 21/7/25</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
   <si>
     <t>Dia</t>
   </si>
@@ -57,9 +54,6 @@
     <t>Lunes</t>
   </si>
   <si>
-    <t>Calle 1211 Y 1244</t>
-  </si>
-  <si>
     <t>Oscar M.</t>
   </si>
   <si>
@@ -69,24 +63,15 @@
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t>Casa America</t>
-  </si>
-  <si>
     <t>Joaquin B.</t>
   </si>
   <si>
     <t>Martes</t>
   </si>
   <si>
-    <t>Calle 1282 Y 1211</t>
-  </si>
-  <si>
     <t>Horacio F.</t>
   </si>
   <si>
-    <t>Calle 1149 Y 1138</t>
-  </si>
-  <si>
     <t>Tobias B.</t>
   </si>
   <si>
@@ -96,18 +81,12 @@
     <t>Rodolfo P.</t>
   </si>
   <si>
-    <t>Calle 1155 Y 1150</t>
-  </si>
-  <si>
     <t>Benjamin S.</t>
   </si>
   <si>
     <t>Jueves</t>
   </si>
   <si>
-    <t>Calle 1211 Y 1286</t>
-  </si>
-  <si>
     <t>Dylan F.</t>
   </si>
   <si>
@@ -129,29 +108,62 @@
     <t>Sabado</t>
   </si>
   <si>
-    <t>Casa Paola Da Fonseca</t>
-  </si>
-  <si>
-    <t>Miguel C.</t>
-  </si>
-  <si>
-    <t>Casa Esther Altamirano</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Calle 1155 Y 1142</t>
-  </si>
-  <si>
     <t>Pablo L.</t>
+  </si>
+  <si>
+    <t>Calle 1282 Y 1213</t>
+  </si>
+  <si>
+    <t>Calle 1149 Y 1134</t>
+  </si>
+  <si>
+    <t>Calle 1209 Y 1268</t>
+  </si>
+  <si>
+    <t>Calle 1155 Y 1138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle 1149 Y 1136 </t>
+  </si>
+  <si>
+    <t>Calle 1215 Y 1286</t>
+  </si>
+  <si>
+    <t>Calle 1149 Y 1122</t>
+  </si>
+  <si>
+    <t>Calle 1282 Y 1201</t>
+  </si>
+  <si>
+    <t>Calle 616 Y Av Ing Allan</t>
+  </si>
+  <si>
+    <t>Ivan M.</t>
+  </si>
+  <si>
+    <t>G1,G2 Y G4</t>
+  </si>
+  <si>
+    <t>Calle 614 Y Av Ing Allan</t>
+  </si>
+  <si>
+    <t>G3 Y G5</t>
+  </si>
+  <si>
+    <t>Alejandro P.</t>
+  </si>
+  <si>
+    <t>Calle 1155 Y 1144</t>
+  </si>
+  <si>
+    <t>SALIDAS DE PREDICACIÓN SEMANA DEL 28/7/25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,19 +640,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="8.7109375" style="1"/>
-    <col min="3" max="3" width="8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7421875" style="1"/>
+    <col min="3" max="3" width="7.93359375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5078125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.76171875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B2" s="17" t="s">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -648,290 +660,290 @@
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
     </row>
-    <row r="3" spans="2:9">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B4" s="6" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="7">
         <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E4" s="6">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E5" s="8">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C6" s="7">
         <v>0.41666666666666669</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E6" s="6">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7">
         <v>0.41666666666666669</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E8" s="3">
         <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C10" s="7">
         <v>0.41666666666666669</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E10" s="6">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C11" s="9">
         <v>0.66666666666666663</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E11" s="5">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C12" s="7">
         <v>0.75</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E12" s="19"/>
       <c r="F12" s="6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C13" s="11">
         <v>0.41666666666666669</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E13" s="14">
         <v>13</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C14" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" s="13">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B15" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C15" s="12">
         <v>0.41666666666666669</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" s="13">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B16" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C16" s="12">
         <v>0.66666666666666663</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E16" s="13">
         <v>22</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="13"/>
@@ -939,9 +951,9 @@
       <c r="F17" s="13"/>
       <c r="G17" s="13"/>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="13"/>
